--- a/test/fixtures/xlsx/doc-showcase/doc-showcase.xlsx
+++ b/test/fixtures/xlsx/doc-showcase/doc-showcase.xlsx
@@ -8,16 +8,21 @@
   <sheets>
     <sheet name="Basics" sheetId="1" r:id="rId3"/>
     <sheet name="Potion" sheetId="2" r:id="rId4"/>
-    <sheet name="Shop" sheetId="3" r:id="rId5"/>
-    <sheet name="Loot" sheetId="4" r:id="rId6"/>
-    <sheet name="Spawn" sheetId="5" r:id="rId7"/>
-    <sheet name="StageReward" sheetId="6" r:id="rId8"/>
+    <sheet name="Types" sheetId="3" r:id="rId5"/>
+    <sheet name="Index" sheetId="4" r:id="rId6"/>
+    <sheet name="Shop" sheetId="5" r:id="rId7"/>
+    <sheet name="Loot" sheetId="6" r:id="rId8"/>
+    <sheet name="Spawn" sheetId="7" r:id="rId9"/>
+    <sheet name="Quest" sheetId="8" r:id="rId10"/>
+    <sheet name="Sides" sheetId="9" r:id="rId11"/>
+    <sheet name="Price" sheetId="10" r:id="rId12"/>
+    <sheet name="Skill" sheetId="11" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="332">
   <si>
     <t xml:space="preserve">:enum Rarity</t>
   </si>
@@ -64,6 +69,33 @@
     <t xml:space="preserve">from bosses</t>
   </si>
   <si>
+    <t xml:space="preserve">:enum Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a potion is made of.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fire_ball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ice_shard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chills</t>
+  </si>
+  <si>
     <t xml:space="preserve">:const Balance</t>
   </si>
   <si>
@@ -163,6 +195,357 @@
     <t xml:space="preserve">900</t>
   </si>
   <si>
+    <t xml:space="preserve">:table Sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One column per scalar type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bigint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64 bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">double</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y or N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At</t>
+  </si>
+  <si>
+    <t xml:space="preserve">datetime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a moment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Span</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timespan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uuid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">an identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9007199254740993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-24 10:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02:03:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7b7d9f6a-1e2c-4c1a-9a5f-2b6d0c3e4f51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1e-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1999-12-31 23:59:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:00:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0f8fad5b-d9cb-469f-a165-70867728950e</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2000-01-01 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00000000-0000-0000-0000-000000000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Marker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Values written as one cell and read as several.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vec3f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">three floats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vec2i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two ints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">color32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">four bytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5, -2, 0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3, 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#FF8000FF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0, 0, 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0, 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#00000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.25, 12, 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1, 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#3366CCFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A flag set beside the number it becomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bitset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which bits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the same value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0b1011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x1f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0b1010_1010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strings that are for something.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string (text)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shown to a player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string (asset=icon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">names a file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You feel better.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon_Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing happens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon_Shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The bottle is empty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Animation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed by name, with a second key beside it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Slot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secondary index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columns numbered so the file names them rather than counts them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">index@1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name@2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#OldColour@3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dropped, and its number reserved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price@4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">added after the drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
     <t xml:space="preserve">:table Shop</t>
   </si>
   <si>
@@ -211,12 +594,57 @@
     <t xml:space="preserve">how many</t>
   </si>
   <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
     <t xml:space="preserve">5</t>
   </si>
   <si>
+    <t xml:space="preserve">:table Craft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The four shapes a reference takes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a whole row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResultName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Potion.Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">one of its values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Potion[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">several rows in one cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substitute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Potion?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a row, or none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1</t>
+  </si>
+  <si>
     <t xml:space="preserve">:table Loot</t>
   </si>
   <si>
@@ -250,9 +678,6 @@
     <t xml:space="preserve">70</t>
   </si>
   <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
     <t xml:space="preserve">potion;rare</t>
   </si>
   <si>
@@ -265,6 +690,45 @@
     <t xml:space="preserve">95</t>
   </si>
   <si>
+    <t xml:space="preserve">:table Drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An array of enums, and one whose elements may be absent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rarity[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which grades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int?[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">how many of each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common;Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">note to self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common;Common</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3;-</t>
+  </si>
+  <si>
     <t xml:space="preserve">:table Spawn</t>
   </si>
   <si>
@@ -301,12 +765,6 @@
     <t xml:space="preserve">2.5</t>
   </si>
   <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
     <t xml:space="preserve">-8.25</t>
   </si>
   <si>
@@ -316,6 +774,93 @@
     <t xml:space="preserve">6</t>
   </si>
   <si>
+    <t xml:space="preserve">:table Deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An array of records, and a record inside a record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot[0].Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot[0].Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot[1].Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot[1].Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home.At.X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two levels in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home.At.Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Quest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One record over several rows, as many as it has rewards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reward[].id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">an element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reward[].count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
     <t xml:space="preserve">:table StageReward(key="Stage,Rank")</t>
   </si>
   <si>
@@ -365,6 +910,114 @@
   </si>
   <si>
     <t xml:space="preserve">stage2_common</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table ServerTuning(side=s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The client build has no type for this at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what it tunes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">how much</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One column of Amount reaches the build; the others do not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what it costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every variant's members side by side; a row fills its own.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect.$type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which shape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect.Chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect.Damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect.Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DamageEffect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealEffect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoEffect</t>
   </si>
 </sst>
 </file>
@@ -409,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:K6"/>
+  <dimension ref="B2:P6"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -425,6 +1078,12 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
@@ -443,15 +1102,27 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
         <v>4</v>
       </c>
-      <c r="K3" t="s">
+      <c r="P3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -466,16 +1137,25 @@
         <v>8</v>
       </c>
       <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
         <v>19</v>
       </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -489,16 +1169,25 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
+        <v>21</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -510,6 +1199,354 @@
       </c>
       <c r="E6" t="s">
         <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:G10"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" t="s">
+        <v>312</v>
+      </c>
+      <c r="G7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>314</v>
+      </c>
+      <c r="G8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>317</v>
+      </c>
+      <c r="G10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:H9"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G3" t="s">
+        <v>324</v>
+      </c>
+      <c r="H3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>328</v>
+      </c>
+      <c r="E8" t="s">
+        <v>329</v>
+      </c>
+      <c r="F8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>330</v>
+      </c>
+      <c r="E9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -524,10 +1561,10 @@
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -535,67 +1572,67 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -603,13 +1640,13 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -617,13 +1654,13 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -631,13 +1668,13 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -647,21 +1684,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:J9"/>
+  <dimension ref="B2:AA9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="M2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N2" t="s">
+        <v>101</v>
+      </c>
+      <c r="S2" t="s">
+        <v>120</v>
+      </c>
+      <c r="T2" t="s">
+        <v>121</v>
+      </c>
+      <c r="X2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="3">
@@ -669,103 +1718,283 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>62</v>
       </c>
       <c r="F3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" t="s">
-        <v>62</v>
+      <c r="N3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P3" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>108</v>
+      </c>
+      <c r="S3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3" t="s">
+        <v>41</v>
+      </c>
+      <c r="U3" t="s">
+        <v>122</v>
+      </c>
+      <c r="V3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
       </c>
       <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" t="s">
+        <v>78</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="O4" t="s">
+        <v>103</v>
+      </c>
+      <c r="P4" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S4" t="s">
+        <v>38</v>
+      </c>
+      <c r="T4" t="s">
+        <v>29</v>
+      </c>
+      <c r="U4" t="s">
+        <v>123</v>
+      </c>
+      <c r="V4" t="s">
         <v>60</v>
       </c>
-      <c r="J4" t="s">
-        <v>20</v>
+      <c r="X4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s">
-        <v>63</v>
+        <v>76</v>
+      </c>
+      <c r="K5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" t="s">
+        <v>104</v>
+      </c>
+      <c r="P5" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>110</v>
+      </c>
+      <c r="S5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" t="s">
+        <v>124</v>
+      </c>
+      <c r="V5" t="s">
+        <v>126</v>
+      </c>
+      <c r="X5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" t="s">
+        <v>40</v>
+      </c>
+      <c r="T6" t="s">
+        <v>43</v>
+      </c>
+      <c r="U6" t="s">
+        <v>43</v>
+      </c>
+      <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -773,19 +2002,58 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" t="s">
+        <v>82</v>
       </c>
       <c r="G7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" t="s">
+        <v>87</v>
+      </c>
+      <c r="N7" t="s">
         <v>7</v>
       </c>
-      <c r="H7" t="s">
+      <c r="O7" t="s">
+        <v>111</v>
+      </c>
+      <c r="P7" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>113</v>
+      </c>
+      <c r="T7" t="s">
         <v>7</v>
       </c>
-      <c r="I7" t="s">
+      <c r="U7" t="s">
+        <v>127</v>
+      </c>
+      <c r="V7" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y7" t="s">
         <v>7</v>
       </c>
-      <c r="J7" t="s">
-        <v>64</v>
+      <c r="Z7" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="8">
@@ -793,19 +2061,58 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" t="s">
+        <v>90</v>
       </c>
       <c r="G8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" t="s">
+        <v>95</v>
+      </c>
+      <c r="N8" t="s">
         <v>10</v>
       </c>
-      <c r="H8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="O8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P8" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>116</v>
+      </c>
+      <c r="T8" t="s">
         <v>10</v>
       </c>
-      <c r="J8" t="s">
-        <v>65</v>
+      <c r="U8" t="s">
+        <v>129</v>
+      </c>
+      <c r="V8" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="9">
@@ -813,19 +2120,58 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
       </c>
       <c r="G9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" t="s">
+        <v>99</v>
+      </c>
+      <c r="N9" t="s">
         <v>13</v>
       </c>
-      <c r="H9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="O9" t="s">
+        <v>117</v>
+      </c>
+      <c r="P9" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>119</v>
+      </c>
+      <c r="T9" t="s">
         <v>13</v>
       </c>
-      <c r="J9" t="s">
-        <v>7</v>
+      <c r="U9" t="s">
+        <v>131</v>
+      </c>
+      <c r="V9" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -835,15 +2181,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:F9"/>
+  <dimension ref="B2:K9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>147</v>
+      </c>
+      <c r="G2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H2" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="3">
@@ -851,109 +2203,184 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" t="s">
-        <v>73</v>
+        <v>150</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
       <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" t="s">
-        <v>74</v>
+        <v>151</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
       <c r="E7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" t="s">
-        <v>77</v>
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J7" t="s">
+        <v>166</v>
+      </c>
+      <c r="K7" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
       <c r="E8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" t="s">
-        <v>79</v>
+        <v>154</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>168</v>
+      </c>
+      <c r="J8" t="s">
+        <v>169</v>
+      </c>
+      <c r="K8" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
       <c r="E9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" t="s">
-        <v>81</v>
+        <v>156</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J9" t="s">
+        <v>172</v>
+      </c>
+      <c r="K9" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -963,15 +2390,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:F9"/>
+  <dimension ref="B2:P9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>175</v>
+      </c>
+      <c r="F2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" t="s">
+        <v>181</v>
+      </c>
+      <c r="K2" t="s">
+        <v>191</v>
+      </c>
+      <c r="L2" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="3">
@@ -979,67 +2418,175 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N3" t="s">
+        <v>195</v>
+      </c>
+      <c r="O3" t="s">
+        <v>198</v>
+      </c>
+      <c r="P3" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I4" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>186</v>
+      </c>
+      <c r="N4" t="s">
+        <v>196</v>
+      </c>
+      <c r="O4" t="s">
+        <v>199</v>
+      </c>
+      <c r="P4" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I5" t="s">
+        <v>187</v>
+      </c>
+      <c r="J5" t="s">
+        <v>189</v>
+      </c>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s">
+        <v>194</v>
+      </c>
+      <c r="N5" t="s">
+        <v>197</v>
+      </c>
+      <c r="O5" t="s">
+        <v>200</v>
+      </c>
+      <c r="P5" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -1047,13 +2594,34 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" t="s">
-        <v>93</v>
+        <v>177</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" t="s">
+        <v>170</v>
+      </c>
+      <c r="L7" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O7" t="s">
+        <v>204</v>
+      </c>
+      <c r="P7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1061,13 +2629,34 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" t="s">
-        <v>95</v>
+        <v>178</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" t="s">
+        <v>190</v>
+      </c>
+      <c r="L8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" t="s">
+        <v>10</v>
+      </c>
+      <c r="O8" t="s">
+        <v>7</v>
+      </c>
+      <c r="P8" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="9">
@@ -1075,13 +2664,34 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" t="s">
-        <v>98</v>
+        <v>179</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" t="s">
+        <v>7</v>
+      </c>
+      <c r="O9" t="s">
+        <v>206</v>
+      </c>
+      <c r="P9" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1091,15 +2701,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:F9"/>
+  <dimension ref="B2:K9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>208</v>
+      </c>
+      <c r="G2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="3">
@@ -1107,67 +2723,118 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>214</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K3" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>36</v>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>225</v>
+      </c>
+      <c r="J4" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>215</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J5" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -1175,13 +2842,703 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E7" t="s">
+        <v>217</v>
+      </c>
+      <c r="F7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" t="s">
+        <v>231</v>
+      </c>
+      <c r="J7" t="s">
+        <v>204</v>
+      </c>
+      <c r="K7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" t="s">
+        <v>219</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" t="s">
+        <v>190</v>
+      </c>
+      <c r="K8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J9" t="s">
+        <v>234</v>
+      </c>
+      <c r="K9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:N9"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>252</v>
+      </c>
+      <c r="J3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K3" t="s">
+        <v>255</v>
+      </c>
+      <c r="L3" t="s">
+        <v>257</v>
+      </c>
+      <c r="M3" t="s">
+        <v>258</v>
+      </c>
+      <c r="N3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" t="s">
+        <v>243</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J5" t="s">
+        <v>253</v>
+      </c>
+      <c r="K5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L5" t="s">
+        <v>256</v>
+      </c>
+      <c r="M5" t="s">
+        <v>259</v>
+      </c>
+      <c r="N5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F7" t="s">
+        <v>246</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" t="s">
+        <v>167</v>
+      </c>
+      <c r="J7" t="s">
+        <v>261</v>
+      </c>
+      <c r="K7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" t="s">
+        <v>262</v>
+      </c>
+      <c r="M7" t="s">
+        <v>81</v>
+      </c>
+      <c r="N7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>170</v>
+      </c>
+      <c r="J8" t="s">
+        <v>264</v>
+      </c>
+      <c r="K8" t="s">
+        <v>265</v>
+      </c>
+      <c r="L8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F9" t="s">
+        <v>249</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>173</v>
+      </c>
+      <c r="J9" t="s">
+        <v>267</v>
+      </c>
+      <c r="K9" t="s">
+        <v>130</v>
+      </c>
+      <c r="L9" t="s">
+        <v>268</v>
+      </c>
+      <c r="M9" t="s">
+        <v>247</v>
+      </c>
+      <c r="N9" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:F12"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>277</v>
+      </c>
+      <c r="E10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:K9"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D5" t="s">
+        <v>284</v>
+      </c>
+      <c r="E5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F5" t="s">
+        <v>288</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s">
+        <v>299</v>
+      </c>
+      <c r="K5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
+        <v>291</v>
+      </c>
+      <c r="I7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" t="s">
+        <v>302</v>
+      </c>
+      <c r="K7" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="8">
@@ -1192,10 +3549,19 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>292</v>
       </c>
       <c r="F8" t="s">
-        <v>113</v>
+        <v>293</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" t="s">
+        <v>304</v>
+      </c>
+      <c r="K8" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="9">
@@ -1206,10 +3572,19 @@
         <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>114</v>
+        <v>294</v>
       </c>
       <c r="F9" t="s">
-        <v>115</v>
+        <v>295</v>
+      </c>
+      <c r="I9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" t="s">
+        <v>305</v>
+      </c>
+      <c r="K9" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
